--- a/appium-tests/appium_test_cases_report.xlsx
+++ b/appium-tests/appium_test_cases_report.xlsx
@@ -20,7 +20,7 @@
     <t>Report Generation Date:</t>
   </si>
   <si>
-    <t>11/8/2026</t>
+    <t>12/8/2026</t>
   </si>
   <si>
     <t>Target:</t>
